--- a/results/full_medical_summary/medical_PartialAbstention_summary.xlsx
+++ b/results/full_medical_summary/medical_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.2382±0.0282</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.1947±0.0327</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.2459±0.0231</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.3072±0.0217</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9924±0.0008</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9737±0.0025</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.8932±0.0069</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.7519±0.0079</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.8626±0.0158</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.6461±0.0274</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.2590±0.0200</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.0914±0.0087</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.8507±0.0150</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.8697±0.0164</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.8419±0.0292</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.7706±0.0365</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.8456±0.0164</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.7007±0.0228</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.3595±0.0226</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.1574±0.0125</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.9897±0.0013</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.9658±0.0031</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.8633±0.0084</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.7206±0.0059</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.8214±0.0193</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6279±0.0263</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.2543±0.0194</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.0906±0.0087</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.3138±0.0174</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.2854±0.0187</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.1658±0.0109</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.0992±0.0074</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.3251±0.0145</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.2405±0.0215</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1145±0.0080</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.0630±0.0051</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.3158±0.0181</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.3950±0.0368</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.4086±0.0367</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.3967±0.0382</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9948±0.0048</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9239±0.0232</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.7854±0.0370</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.8417±0.0182</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6324±0.0240</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.2965±0.0188</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1449±0.0095</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.8460±0.0188</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.4937±0.0260</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.1791±0.0131</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.0798±0.0054</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.8375±0.0189</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.8809±0.0179</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.8636±0.0251</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.7887±0.0360</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.7730±0.0217</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.4587±0.0397</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.0661±0.0139</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.0027±0.0036</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.7489±0.0292</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.4381±0.0397</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.0585±0.0121</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.0022±0.0036</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.2300±0.0311</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.1901±0.0327</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.2515±0.0238</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.3209±0.0206</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9926±0.0009</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9686±0.0026</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.8741±0.0075</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.7236±0.0081</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.8633±0.0194</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.6007±0.0235</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.2277±0.0184</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.0849±0.0081</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8661±0.0168</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.8773±0.0160</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.8546±0.0267</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7859±0.0342</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.8529±0.0191</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.6682±0.0208</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.3267±0.0212</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.1474±0.0115</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.9901±0.0015</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.9594±0.0030</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.8400±0.0089</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6905±0.0058</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.8271±0.0223</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.5863±0.0236</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.2244±0.0182</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.0843±0.0080</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.3205±0.0136</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.2727±0.0191</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.1555±0.0098</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.0945±0.0064</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.3320±0.0130</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.2220±0.0214</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.1052±0.0072</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.0592±0.0043</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.3258±0.0168</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.4059±0.0378</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.4219±0.0358</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.4103±0.0376</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9926±0.0056</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9024±0.0282</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7615±0.0446</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.8486±0.0204</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.5934±0.0230</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.2669±0.0166</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1346±0.0082</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.8408±0.0198</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.4450±0.0231</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.1575±0.0112</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.0734±0.0046</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.8568±0.0227</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.8912±0.0185</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.8773±0.0227</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.8047±0.0341</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.7730±0.0278</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.4002±0.0319</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.0505±0.0151</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.0027±0.0036</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.7497±0.0352</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.3787±0.0311</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.0433±0.0123</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.0022±0.0036</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.2382±0.0282</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.1953±0.0325</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.2471±0.0253</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.3060±0.0238</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9924±0.0008</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9736±0.0024</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.8933±0.0070</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.7522±0.0076</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.8632±0.0166</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.6454±0.0272</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.2586±0.0204</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.0908±0.0087</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.8495±0.0165</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.8672±0.0163</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.8401±0.0294</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.7634±0.0361</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.8454±0.0172</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.6991±0.0228</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.3590±0.0232</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.1564±0.0124</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.9897±0.0013</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.9657±0.0031</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.8633±0.0085</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.7209±0.0055</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.8215±0.0195</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.6265±0.0261</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.2539±0.0198</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.0901±0.0086</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.3140±0.0172</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.2848±0.0189</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.1658±0.0112</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.0985±0.0072</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.3255±0.0142</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.2403±0.0216</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1147±0.0082</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.0627±0.0050</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.3157±0.0182</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.3938±0.0368</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.4069±0.0369</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.3935±0.0372</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9948±0.0052</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9244±0.0222</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.7850±0.0424</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.8419±0.0189</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6309±0.0239</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.2962±0.0192</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.1438±0.0094</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.8474±0.0188</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.4927±0.0258</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.1790±0.0134</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.0792±0.0053</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.8365±0.0201</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.8778±0.0179</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.8613±0.0255</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.7808±0.0355</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.7740±0.0199</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.4577±0.0384</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.0661±0.0140</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.0027±0.0036</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.7500±0.0271</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.4370±0.0384</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.0585±0.0127</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.0022±0.0036</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.2346±0.0258</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.1898±0.0322</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.2523±0.0269</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.3197±0.0209</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9925±0.0008</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9686±0.0026</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.8740±0.0079</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.7234±0.0084</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.8605±0.0193</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.5999±0.0230</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.2282±0.0190</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.0845±0.0081</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.8645±0.0176</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.8769±0.0167</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.8532±0.0272</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.7836±0.0337</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.8504±0.0189</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.6678±0.0209</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.3267±0.0216</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.1469±0.0115</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.9899±0.0014</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.9594±0.0030</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.8398±0.0092</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6901±0.0058</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.8238±0.0218</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.5859±0.0236</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.2247±0.0182</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.0839±0.0080</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.3203±0.0138</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.2726±0.0190</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.1554±0.0103</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.0943±0.0068</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.3315±0.0126</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.2219±0.0213</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1052±0.0076</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.0591±0.0046</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.3258±0.0170</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.4047±0.0388</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.4212±0.0365</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.4099±0.0375</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9918±0.0062</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9014±0.0284</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.7596±0.0456</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.8467±0.0192</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.5931±0.0233</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.2665±0.0170</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.1341±0.0083</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.8377±0.0188</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.4448±0.0231</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.1573±0.0114</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.0732±0.0047</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.8560±0.0218</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.8909±0.0191</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.8755±0.0229</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.8014±0.0334</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.7679±0.0263</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.4004±0.0315</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.0513±0.0146</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.0025±0.0033</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.7442±0.0348</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.3783±0.0309</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.0439±0.0118</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.0020±0.0032</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.2607±0.0339</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.2119±0.0331</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.2540±0.0275</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.3010±0.0263</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9923±0.0010</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9769±0.0021</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.9106±0.0061</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.7846±0.0083</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.8683±0.0172</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.6872±0.0239</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.3173±0.0219</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.1055±0.0101</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.8423±0.0232</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.8638±0.0184</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.8338±0.0224</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.7623±0.0373</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.8437±0.0217</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.7277±0.0194</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.4144±0.0220</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.1790±0.0145</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.9896±0.0014</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.9723±0.0026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.8988±0.0066</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.7784±0.0078</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.8190±0.0253</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.6620±0.0220</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.3080±0.0213</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.1043±0.0100</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.3068±0.0131</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.2967±0.0222</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.1793±0.0109</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.1070±0.0085</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.3217±0.0121</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.2560±0.0256</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1271±0.0082</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.0695±0.0059</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.3070±0.0156</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.3919±0.0343</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.3961±0.0385</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.3774±0.0421</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.9973±0.0040</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9509±0.0170</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8466±0.0237</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.8390±0.0214</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.6627±0.0208</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3353±0.0192</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1628±0.0121</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.8560±0.0196</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.5364±0.0245</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.2094±0.0142</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.0912±0.0071</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.8229±0.0255</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.8678±0.0157</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.8429±0.0230</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.7603±0.0358</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.7700±0.0303</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.5037±0.0352</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.0980±0.0210</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.0012±0.0030</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.7453±0.0369</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.4880±0.0350</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.0939±0.0187</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.0012±0.0030</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.2436±0.0298</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.2010±0.0360</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.2547±0.0280</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.3204±0.0192</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9918±0.0011</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9676±0.0026</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.8695±0.0073</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.6949±0.0088</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.8576±0.0206</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.5956±0.0221</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.2189±0.0156</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.0760±0.0067</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.8601±0.0250</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.8755±0.0203</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.8575±0.0198</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.8101±0.0360</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.8447±0.0241</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.6635±0.0204</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.3179±0.0173</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.1361±0.0107</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.9891±0.0017</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.9613±0.0030</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.8526±0.0077</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.6861±0.0075</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.8156±0.0275</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.5793±0.0218</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.2150±0.0150</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.0755±0.0067</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.3183±0.0128</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.2740±0.0227</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.1540±0.0096</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.0919±0.0065</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.3278±0.0142</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.2226±0.0243</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1037±0.0070</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.0570±0.0043</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.3261±0.0177</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.4109±0.0415</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.4242±0.0382</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.4256±0.0408</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.9922±0.0071</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9127±0.0209</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.7546±0.0247</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.8358±0.0222</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.5885±0.0233</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.2631±0.0149</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1273±0.0084</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.8230±0.0195</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.4412±0.0240</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.1550±0.0101</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.0691±0.0047</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.8491±0.0273</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.8848±0.0169</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.8705±0.0201</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.8091±0.0353</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.7546±0.0325</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.3853±0.0302</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.0401±0.0136</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.7292±0.0398</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.3667±0.0292</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.0363±0.0119</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.2640±0.0377</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.2159±0.0338</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.2555±0.0268</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.3009±0.0272</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9922±0.0010</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9781±0.0020</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.9148±0.0057</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.7903±0.0084</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.8683±0.0172</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.7009±0.0236</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.3335±0.0222</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.1086±0.0105</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.8383±0.0253</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.8591±0.0182</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.8265±0.0244</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.7469±0.0389</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.8415±0.0227</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.7363±0.0191</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.4283±0.0228</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.1826±0.0151</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.9895±0.0014</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.9736±0.0025</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.9035±0.0064</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.7841±0.0080</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.8162±0.0261</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.6743±0.0220</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.3232±0.0221</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.1072±0.0105</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.3042±0.0134</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.2990±0.0237</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.1821±0.0118</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.1071±0.0089</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.3214±0.0122</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.2608±0.0269</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1302±0.0087</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.0699±0.0061</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.3034±0.0158</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.3869±0.0363</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.3903±0.0361</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.3693±0.0437</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.9978±0.0039</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9542±0.0167</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.8539±0.0222</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.8361±0.0223</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.6722±0.0203</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3440±0.0201</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1636±0.0123</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.8559±0.0197</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.5514±0.0239</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.2167±0.0149</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.0919±0.0072</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.8173±0.0276</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.8616±0.0167</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.8349±0.0250</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.7451±0.0367</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.7659±0.0305</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.5244±0.0363</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.1119±0.0214</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.0012±0.0030</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.7409±0.0363</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.5092±0.0366</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.1079±0.0194</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.0012±0.0030</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.2487±0.0259</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.2008±0.0359</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.2547±0.0273</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.3183±0.0233</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9923±0.0010</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9675±0.0026</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.8697±0.0076</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.6994±0.0090</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.8629±0.0189</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.5947±0.0217</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.2199±0.0160</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.0761±0.0067</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.8591±0.0226</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.8749±0.0188</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.8561±0.0223</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.8050±0.0375</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.8482±0.0218</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.6623±0.0196</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.3185±0.0180</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.1363±0.0107</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.9896±0.0015</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.9610±0.0030</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.8528±0.0082</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.6903±0.0078</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.8201±0.0252</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.5774±0.0216</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.2158±0.0154</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.0756±0.0067</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.3204±0.0142</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.2743±0.0219</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.1541±0.0101</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.0923±0.0068</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.3323±0.0132</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.2226±0.0236</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1038±0.0072</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.0574±0.0045</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.3252±0.0175</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.4118±0.0423</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.4244±0.0389</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.4223±0.0433</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.9919±0.0075</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9115±0.0215</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.7591±0.0244</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.8431±0.0213</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.5873±0.0225</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.2631±0.0158</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1284±0.0087</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.8411±0.0184</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.4402±0.0232</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.1551±0.0106</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.0698±0.0049</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.8453±0.0258</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.8835±0.0161</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.8691±0.0234</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.8055±0.0370</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.7607±0.0301</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.3814±0.0303</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.0415±0.0147</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.7359±0.0394</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.3626±0.0306</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.0374±0.0126</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
